--- a/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/continuation/conductor_1_input.xlsx
+++ b/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/continuation/conductor_1_input.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAN" sheetId="2" r:id="Rc0e3f1ec685344ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK" sheetId="5" r:id="R15fe2fb27f564caf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_MIX" sheetId="3" r:id="Rdedd5ac2573c4dfb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_STAB" sheetId="6" r:id="R2281f2dea29f4c54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_JACKET" sheetId="4" r:id="R3ce93dc7493b4dca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAN" sheetId="2" r:id="Re56c563535014a65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK" sheetId="5" r:id="Rdb04baf097e94325"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_MIX" sheetId="3" r:id="R245d0069c0d74581"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_STAB" sheetId="6" r:id="Rcc2f2acca7ec43a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_JACKET" sheetId="4" r:id="R8f2da98edfe74bbd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -660,7 +660,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D5" s="48" t="str">
-        <x:v>x coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>x coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E5" s="45" t="n">
         <x:v>0.00197</x:v>
@@ -680,7 +680,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D6" s="48" t="str">
-        <x:v>y coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>y coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E6" s="45" t="n">
         <x:v>0.00812</x:v>
@@ -780,7 +780,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D11" s="48" t="str">
-        <x:v>VIOD FRACTION OF THE CHANNEL = VOID AREA/TOTALAREA OF THE CHANNEL</x:v>
+        <x:v>VOID FRACTION OF THE CHANNEL = VOID AREA / TOTAL AREA OF THE CHANNEL</x:v>
       </x:c>
       <x:c r="E11" s="44" t="n">
         <x:v>1</x:v>
@@ -1482,7 +1482,7 @@
       <x:c r="B2" s="34"/>
       <x:c r="C2" s="34"/>
       <x:c r="D2" s="36" t="str">
-        <x:v>row used to get the correct number of mixed copper-supeconductor strands objects in cell B1 as the sum of values in this row starting from cell D2</x:v>
+        <x:v>Row used to determine the number of mixed copper-superconductor strand objects in cell B1, calculated as the sum of the values in this row starting from cell D2.</x:v>
       </x:c>
       <x:c r="E2" s="32" t="n">
         <x:v>0</x:v>
@@ -1932,7 +1932,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D5" s="48" t="str">
-        <x:v>x coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>x coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E5" s="45" t="n">
         <x:v>0.00204</x:v>
@@ -1955,7 +1955,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D6" s="48" t="str">
-        <x:v>y coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>y coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E6" s="45" t="n">
         <x:v>0.00462</x:v>
@@ -2164,7 +2164,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D6" s="48" t="str">
-        <x:v>x coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>x coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E6" s="45" t="n">
         <x:v>0.00235</x:v>
@@ -2181,7 +2181,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D7" s="48" t="str">
-        <x:v>y coordinate of the barycenter Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>y coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E7" s="45" t="n">
         <x:v>0.01077</x:v>
